--- a/fixtures/C_ALPHA/spec_builder.xlsx
+++ b/fixtures/C_ALPHA/spec_builder.xlsx
@@ -986,7 +986,7 @@
     <t>Plan id *</t>
   </si>
   <si>
-    <t>Plan label *</t>
+    <t>Plan label</t>
   </si>
   <si>
     <t>Network</t>
